--- a/15_機能設計書（APIシーケンス図）/99_参考過去資料/API_15_タッチメニュー設定/40_API設計_AP1507_階層一覧取得.xlsx
+++ b/15_機能設計書（APIシーケンス図）/99_参考過去資料/API_15_タッチメニュー設定/40_API設計_AP1507_階層一覧取得.xlsx
@@ -19530,10 +19530,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010061A9778B95955B468B907ACFDC6C24AA" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="726537ecfb063646cd688700d616079b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c25985f6-738a-4fbb-ade1-fdbe81c9268b" xmlns:ns3="2dd5972e-fc8f-47aa-916d-ced3529f73a8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7f884ee00b5d4c00816d2be8aa57e92" ns2:_="" ns3:_="">
-    <xsd:import namespace="c25985f6-738a-4fbb-ade1-fdbe81c9268b"/>
-    <xsd:import namespace="2dd5972e-fc8f-47aa-916d-ced3529f73a8"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101008AB003DB5A4D644C9FB3BD19B5C7E000" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="14213891138059eb724b9e737fafccea">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="74a0992f-8328-4daf-870b-3d2b13d3e940" xmlns:ns3="4a37abda-15dd-4e37-8275-3b7fb2897b65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c0714e9ec9c019f03b39320eca5a0ecc" ns2:_="" ns3:_="">
+    <xsd:import namespace="74a0992f-8328-4daf-870b-3d2b13d3e940"/>
+    <xsd:import namespace="4a37abda-15dd-4e37-8275-3b7fb2897b65"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -19542,12 +19542,11 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
@@ -19558,7 +19557,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c25985f6-738a-4fbb-ade1-fdbe81c9268b" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="74a0992f-8328-4daf-870b-3d2b13d3e940" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -19571,12 +19570,12 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -19596,19 +19595,14 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="15" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="06bef0e2-ccd2-4e75-9a04-7e89d13ad686" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="e6619b5c-6674-40b7-9c01-33e12ba1bd7c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -19616,10 +19610,10 @@
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2dd5972e-fc8f-47aa-916d-ced3529f73a8" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4a37abda-15dd-4e37-8275-3b7fb2897b65" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{35465f8c-49d0-4f7c-88a6-833fad5fd184}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2dd5972e-fc8f-47aa-916d-ced3529f73a8">
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f2a2e70a-4904-448e-b588-7989bbdb9dd5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4a37abda-15dd-4e37-8275-3b7fb2897b65">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -19739,10 +19733,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4a37abda-15dd-4e37-8275-3b7fb2897b65" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="74a0992f-8328-4daf-870b-3d2b13d3e940">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDE57056-33D1-4CF4-8041-8F9C912EB7EA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9952C1-8A19-4BE4-A570-5CCC8F95639B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4BA4CA6-3732-4266-8238-AF27A7F304CA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A37DA5B-997B-4E82-8DBD-3C4FA089FC7D}"/>
 </file>